--- a/modules/conjoint/examples/example_config.xlsx
+++ b/modules/conjoint/examples/example_config.xlsx
@@ -268,7 +268,7 @@
     <t xml:space="preserve">The data was simulated from known utilities (see README.md); the HB run should recover their order.</t>
   </si>
   <si>
-    <t xml:space="preserve">50 respondents is small for HB, so expect a convergence warning and a PARTIAL status. That is honest, not a fault.</t>
+    <t xml:space="preserve">Expect a PARTIAL status with two data warnings: product combinations never chosen, and 50 respondents below the sample-size rule of thumb. HB also prints a convergence note; that is not what makes the run PARTIAL.</t>
   </si>
 </sst>
 </file>
